--- a/SCRAPING/wisataV2_updated.xlsx
+++ b/SCRAPING/wisataV2_updated.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20TRANS%20Wisata%20Belah%20Duren%20Malang</t>
+          <t>https://www.instagram.com/p/DWDZT_8gadV/</t>
         </is>
       </c>
     </row>
@@ -742,16 +742,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Fishing%20Sultan%20Class%20Malang</t>
+          <t>https://id.trip.com/travel-guide/attraction/ngantang/fishing-sultan-class-142577799?scene=gsDestination</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>225000</v>
+        <v>175000</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DYbh2ofxq03/</t>
+          <t>https://www.instagram.com/reel/DLRspEGRMKQ/</t>
         </is>
       </c>
     </row>
@@ -1507,16 +1507,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Monumen%20Palagan%20Mendalan%20Malang</t>
+          <t>https://id.trip.com/travel-guide/attraction/ngantang/monumen-palagan-mendalan-142335372/</t>
         </is>
       </c>
     </row>
@@ -1554,11 +1554,7 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -2000,11 +1996,7 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2264,16 +2256,16 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>650000</v>
+        <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Gua%20Maria%20Sendang%20Purwaningsih%20Malang</t>
+          <t>https://id.trip.com/travel-guide/attraction/donomulyo/gua-maria-sendang-purwaningsih-137312022/</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2301,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Tempat%20Wisata%20Mancing%20ikan%20air%20tawar%20di%20tengah%20bendungan%20Malang</t>
+          <t>https://www.instagram.com/p/DDeFbG7TR7n/</t>
         </is>
       </c>
     </row>
@@ -2399,16 +2391,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>150000</v>
+        <v>15000</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>waysata.com</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://waysata.com/page/news/taman-merak-pujon-rafting-wisata-alam-dan-petualangan-di-pujon</t>
+          <t>https://id.trip.com/travel-guide/attraction/pujon/taman-merak-pujon-rafting-137962349/</t>
         </is>
       </c>
     </row>
@@ -2939,7 +2931,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>100000</v>
+        <v>195000</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3434,16 +3426,16 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1250000</v>
+        <v>0</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>matic.malangkab.go.id</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Wisata%20Edukasi%20Jowaran%20Malang</t>
+          <t>https://matic.malangkab.go.id/listing/desa-wisata-jambuwer</t>
         </is>
       </c>
     </row>
@@ -3569,16 +3561,16 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Kolam%20Renang%20Centil%20Malang</t>
+          <t>https://www.instagram.com/reel/DEjK_ASvIYE/</t>
         </is>
       </c>
     </row>
@@ -3613,19 +3605,9 @@
           <t>https://www.google.com/maps/place/THR+SUMBERDUREN+KECOPOKAN/data=!4m7!3m6!1s0x2e78a307eb46f091:0x3ef3c7c4ce79a86b!8m2!3d-8.1850538!4d112.4963026!16s%2Fg%2F11j239vxvc!19sChIJkfBG6wejeC4Ra6h5zsTH8z4?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I71" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Google Snippet</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20THR%20SUMBERDUREN%20KECOPOKAN%20Malang</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3659,16 +3641,16 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Wisata%20Rajut%20indah%20Malang</t>
+          <t>https://www.instagram.com/reel/DKevwxKT9tW/</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3956,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>369387</v>
+        <v>0</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -4696,11 +4678,7 @@
       <c r="I95" t="n">
         <v>0</v>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
@@ -5680,16 +5658,16 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Pondok%20Wisata%20Latar%20Ombo%20%22L.O.%22%20Malang</t>
+          <t>https://www.instagram.com/latarombo1/</t>
         </is>
       </c>
     </row>
@@ -5727,11 +5705,7 @@
       <c r="I118" t="n">
         <v>0</v>
       </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
@@ -5991,16 +5965,16 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>127500</v>
+        <v>0</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>tiket.com</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>https://www.tiket.com/id-id/to-do/batu-night-spectacular</t>
+          <t>https://www.instagram.com/p/DQWAfdEE5i1/</t>
         </is>
       </c>
     </row>
@@ -6351,16 +6325,16 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>161500</v>
+        <v>0</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>traveloka.com</t>
+          <t>reddoorz.com</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>https://www.traveloka.com/id-id/activities/indonesia/product/dino-park-tickets-jatim-park-3-2000625477091</t>
+          <t>https://www.reddoorz.com/id-id/blog/places-to-visit/jatim-park-3</t>
         </is>
       </c>
     </row>
@@ -6486,16 +6460,16 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20KLEINE%20HOLLAND%20Malang</t>
+          <t>https://www.instagram.com/p/DXA52tlE8Ac/</t>
         </is>
       </c>
     </row>
@@ -6936,16 +6910,16 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>nagantour.com</t>
+          <t>tiket.com</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>https://nagantour.com/museum-tubuh/</t>
+          <t>https://www.tiket.com/id-id/to-do/museum-tubuh</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7045,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>115000</v>
+        <v>65000</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -7165,12 +7139,12 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>matic.malangkab.go.id</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Taman%20Dancok%20Malang</t>
+          <t>https://matic.malangkab.go.id/listing/cafe-dancok</t>
         </is>
       </c>
     </row>
@@ -7611,16 +7585,16 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>100000</v>
+        <v>275000</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>raftingpujon.com</t>
+          <t>waysata.com</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>https://www.raftingpujon.com/</t>
+          <t>https://waysata.com/page/news/taman-merak-pujon-rafting-wisata-alam-dan-petualangan-di-pujon</t>
         </is>
       </c>
     </row>
@@ -7701,16 +7675,16 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>traveloka.com</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Bukit%20Jengkoang%20Malang</t>
+          <t>https://www.traveloka.com/id-id/explore/destination/mengenal-bukit-jengkoang-inilah-fakta-dan-daya-tarik-wisatanya-acc/535945</t>
         </is>
       </c>
     </row>
@@ -7971,16 +7945,16 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Wisata%20Kebun%20Bunga%20Coban%20Talun%20Malang</t>
+          <t>https://www.instagram.com/reel/DDeesEsp4Xt/</t>
         </is>
       </c>
     </row>
@@ -8016,16 +7990,16 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Wisata%20petik%20strowberry%20kebundesa%28yeni%29%20Malang</t>
+          <t>https://www.instagram.com/reel/DWQ6-FakTmZ/</t>
         </is>
       </c>
     </row>
@@ -8061,16 +8035,16 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>550000</v>
+        <v>0</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>kebun8.com</t>
+          <t>24travel.id</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>https://kebun8.com/paket/off-road/</t>
+          <t>https://24travel.id/brakseng-malang/</t>
         </is>
       </c>
     </row>
@@ -8151,16 +8125,16 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Toko%20taman%20ayu%20nganteb%20%28TAN%29%20Malang</t>
+          <t>https://www.instagram.com/p/CZsx6yhh2o9/</t>
         </is>
       </c>
     </row>
@@ -8693,11 +8667,7 @@
       <c r="I184" t="n">
         <v>0</v>
       </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
@@ -8822,7 +8792,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1800000</v>
+        <v>10000</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -9317,16 +9287,16 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20WISATA%20PETIRTAAN%20KAYGUN%20Malang</t>
+          <t>https://id.trip.com/travel-guide/attraction/batu/wisata-petirtaan-kaygun-136956930/</t>
         </is>
       </c>
     </row>
@@ -9407,16 +9377,16 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>127500</v>
+        <v>0</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>tiket.com</t>
+          <t>jtp.id</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>https://www.tiket.com/id-id/to-do/batu-night-spectacular</t>
+          <t>https://jtp.id/bns/batu-night-spectacular-primadona-wisata-malam-di-kota-malang-dan-batu/index.html</t>
         </is>
       </c>
     </row>
@@ -9497,16 +9467,16 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>wesb-nandhi.com</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Wisata%20Edukasi%20Susu%20Batu%20Malang</t>
+          <t>https://wesb-nandhi.com/</t>
         </is>
       </c>
     </row>
@@ -9542,16 +9512,16 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>175000</v>
+        <v>0</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>facebook.com</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/p/Kampung-Wisata-Tani-Temas-100083374995440/</t>
+          <t>https://www.instagram.com/p/DPGroxwEZVK/</t>
         </is>
       </c>
     </row>
@@ -9812,16 +9782,16 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>tiket.com</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>https://www.tiket.com/id-id/to-do/jatim-park-2</t>
+          <t>https://www.instagram.com/reel/Cu6kYWHJdFo/?hl=id</t>
         </is>
       </c>
     </row>
@@ -9902,16 +9872,16 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>kaliwatu.co.id</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Batu%20Rafting%20Malang</t>
+          <t>https://kaliwatu.co.id/rafting-di-batu-malang/</t>
         </is>
       </c>
     </row>
@@ -9947,16 +9917,16 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>tiket.com</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>https://www.tiket.com/id-id/to-do/jatim-park-2</t>
+          <t>https://www.instagram.com/jatimparkdua/</t>
         </is>
       </c>
     </row>
@@ -10172,16 +10142,16 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>108900</v>
+        <v>0</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Museum%20Angkut%20Malang</t>
+          <t>https://www.instagram.com/museumangkut/</t>
         </is>
       </c>
     </row>
@@ -10221,12 +10191,12 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>labirutour.com</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Kaliwatu%20Rafting%20Malang</t>
+          <t>https://labirutour.com/obyek-wisata/malang-rafting-kaliwatu</t>
         </is>
       </c>
     </row>
@@ -10262,16 +10232,16 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>165000</v>
+        <v>0</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>tiket.com</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>https://www.tiket.com/id-id/to-do/batu-love-garden</t>
+          <t>https://www.instagram.com/reel/DMCyFhPP3Wk/</t>
         </is>
       </c>
     </row>
@@ -10352,16 +10322,16 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>112200</v>
+        <v>0</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>tiket.com</t>
+          <t>traveloka.com</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>https://www.tiket.com/id-id/to-do/museum-angkut</t>
+          <t>https://www.traveloka.com/id-id/explore/destination/pasar-apung-batu-tradisi-unik-di-indonesia-acc/496849</t>
         </is>
       </c>
     </row>
@@ -10487,16 +10457,16 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>id.trip.com</t>
+          <t>tripadvisor.co.id</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>https://id.trip.com/guide/attraction/tempat-wisata-terbaik-di-batu.html</t>
+          <t>https://www.tripadvisor.co.id/Attraction_Review-g1237079-d3377122-Reviews-Omah_Budaya_Slamet-Batu_East_Java_Java.html</t>
         </is>
       </c>
     </row>
@@ -10669,11 +10639,7 @@
       <c r="I228" t="n">
         <v>0</v>
       </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
@@ -10982,12 +10948,12 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Tiara%20Apel%20%28Lokasi%20kebun%20pindah2%2C%20minta%20sharelok%20admin%20saja%29%20Malang</t>
+          <t>https://www.instagram.com/reel/DRnzrlQk3Qd/</t>
         </is>
       </c>
     </row>
@@ -11023,16 +10989,16 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>traveloka.com</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Petik%20apel%20malang%20%26%20petik%20jeruk%20keprok%20%22BATU%20AGRO%20APEL%22%20kota%20batu%2C%20malang%20Malang</t>
+          <t>https://www.traveloka.com/id-id/explore/destination/wisata-petik-apel-malang-acc/469830</t>
         </is>
       </c>
     </row>
@@ -11203,16 +11169,16 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Tabebuia%20tree%20%26%20Plants%20Suplier%20Landscape%20by%20Roseasterina%20jual%20/%20sell%20Pohon%20Malang</t>
+          <t>https://id.trip.com/travel-guide/attraction/batu/wisata-petik-mawar-desa-gunungsari-jual-bunga-mawar-taman-bunga-foto-taman-mawar-indah-terdekat-138029210/</t>
         </is>
       </c>
     </row>
@@ -11653,16 +11619,16 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1750000</v>
+        <v>0</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>liburan.gustibalitours.com</t>
+          <t>traveloka.com</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>https://www.liburan.gustibalitours.com/produk/paket-tirta-yatra-bromo-malang/</t>
+          <t>https://www.traveloka.com/id-id/explore/activities/pura-di-malang-ta/505352</t>
         </is>
       </c>
     </row>
@@ -11878,16 +11844,16 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>sidita.disbudpar.jatimprov.go.id</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20REST%20AREA%20TAWON%20Malang</t>
+          <t>https://sidita.disbudpar.jatimprov.go.id/destinasi/detail/360fc66ea54c2c5028bfdfb64661bd665d625ede5eb33e9ea2fe5ac79e670a6aa78e845b60f511c444d2bbf1318fdb10ca78e357852c10b77fa6a3818367167d</t>
         </is>
       </c>
     </row>
@@ -12193,16 +12159,16 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>atourin.com</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Penyebrangan%20Jurang%20Toleh%20Malang</t>
+          <t>https://atourin.com/destination/malang/taman-jurang-toleh</t>
         </is>
       </c>
     </row>
@@ -12328,16 +12294,16 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>gotravelly.com</t>
+          <t>matic.malangkab.go.id</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>https://www.gotravelly.com/blog/6-rekomendasi-wisata-religi-malang-paling-ramai-pengunjung/</t>
+          <t>https://matic.malangkab.go.id/listing/monumen-peniwen-affair</t>
         </is>
       </c>
     </row>
@@ -12778,16 +12744,16 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>waze.com</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Unimaz%20Rajut%20Malang</t>
+          <t>https://www.waze.com/id/live-map/directions/id/jawa-timur/toko-benang-rajut-julia-house?to=place.ChIJ6SM0niUo1i0RQPl1QGFpZ1A</t>
         </is>
       </c>
     </row>
@@ -12915,11 +12881,7 @@
       <c r="I278" t="n">
         <v>0</v>
       </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
@@ -13269,16 +13231,16 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>215000</v>
+        <v>195000</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>labirutour.com</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Rafting%20Sahabat%20Air%20Malang</t>
+          <t>https://labirutour.com/obyek-wisata/malang-rafting-kaliwatu</t>
         </is>
       </c>
     </row>
@@ -13314,16 +13276,16 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>binus.ac.id</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Museum%20Art%20Gallery%20Malang</t>
+          <t>https://binus.ac.id/malang/dkv/2023/06/05/semeru-art-gallery-malang-an-overview-by-jennifer/</t>
         </is>
       </c>
     </row>
@@ -13359,16 +13321,16 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Kampoeng%20Wisata%20De%20Berran%20Malang</t>
+          <t>https://www.instagram.com/p/C27LxGWLJiu/</t>
         </is>
       </c>
     </row>
@@ -13584,16 +13546,16 @@
         </is>
       </c>
       <c r="I293" t="n">
-        <v>300000</v>
+        <v>7500</v>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>ronapersadatour.com</t>
+          <t>offroadcobantalun.com</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>https://ronapersadatour.com/offroad-batu-malang/</t>
+          <t>https://offroadcobantalun.com/</t>
         </is>
       </c>
     </row>
@@ -14169,16 +14131,16 @@
         </is>
       </c>
       <c r="I306" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>sidita.disbudpar.jatimprov.go.id</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Mie%20ayam%20kali%20mbureng%20Malang</t>
+          <t>https://sidita.disbudpar.jatimprov.go.id/destinasi/detail/a8beb30b9c8e3b868e66bbe97b9f615567b69dda10fee72ceea1e4ca4523259080974a4bbfa0cb95f42ace13b4ab85c53897546807c8653ee1586059e62f4c3c-2</t>
         </is>
       </c>
     </row>
@@ -14439,16 +14401,16 @@
         </is>
       </c>
       <c r="I312" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>niagatour.com</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Taman%20Trunojoyo%20Malang</t>
+          <t>https://niagatour.com/taman-trunojoyo-malang/</t>
         </is>
       </c>
     </row>
@@ -14666,11 +14628,7 @@
       <c r="I317" t="n">
         <v>0</v>
       </c>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
@@ -14844,12 +14802,12 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Idjen%20Boulevard%20Malang</t>
+          <t>https://id.trip.com/travel-guide/attraction/klojen/idjen-boulevard-61142513/</t>
         </is>
       </c>
     </row>
@@ -14930,16 +14888,16 @@
         </is>
       </c>
       <c r="I323" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>malangkota.go.id</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Taman%20Dempo%20Malang</t>
+          <t>https://malangkota.go.id/2017/12/24/diresmikan-taman-dempo-jadi-kado-akhir-tahun/</t>
         </is>
       </c>
     </row>
@@ -15110,16 +15068,16 @@
         </is>
       </c>
       <c r="I327" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>instagram.com</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ppmajmalang/</t>
+          <t>https://id.trip.com/travel-guide/attraction/klojen/malang-jami-grand-mosque-104147820/</t>
         </is>
       </c>
     </row>
@@ -15515,16 +15473,16 @@
         </is>
       </c>
       <c r="I336" t="n">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20EXTREME%20SPORTS%20CENTER%20INDONESIA%20Malang</t>
+          <t>https://www.instagram.com/p/DXAz5uuvnqV/</t>
         </is>
       </c>
     </row>
@@ -15605,16 +15563,16 @@
         </is>
       </c>
       <c r="I338" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>lemon8-app.com</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Taman%20Terapi%20%28ITP%29%20Malang</t>
+          <t>https://www.lemon8-app.com/@resha.rizky/7582794170150945298?region=id</t>
         </is>
       </c>
     </row>
@@ -15965,16 +15923,16 @@
         </is>
       </c>
       <c r="I346" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>tiket.com</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>https://www.tiket.com/id-id/to-do/jatim-park-2</t>
+          <t>https://www.instagram.com/jatimparkdua/</t>
         </is>
       </c>
     </row>
@@ -16010,16 +15968,16 @@
         </is>
       </c>
       <c r="I347" t="n">
-        <v>115000</v>
+        <v>0</v>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>jtp.id</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Museum%20D%27Topeng%20Kingdom%20%28INDONESIAN%20HERITAGE%20MUSEUM%29%20Jatim%20Park%201%20Malang</t>
+          <t>https://jtp.id/jatimpark1/get-to-know-more-jawa-timur-park-1/index.html</t>
         </is>
       </c>
     </row>
@@ -16237,11 +16195,7 @@
       <c r="I352" t="n">
         <v>0</v>
       </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J352" t="inlineStr"/>
       <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
@@ -16276,16 +16230,16 @@
         </is>
       </c>
       <c r="I353" t="n">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>kebun8.com</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Rest%20Area%20Wisata%20Petik%20Apel%20%22Mitra%20Apel%22%20Malang</t>
+          <t>https://kebun8.com/paket/petik-apel/</t>
         </is>
       </c>
     </row>
@@ -16681,16 +16635,16 @@
         </is>
       </c>
       <c r="I362" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Pantai%20Gopit%20%EA%A6%A5%EA%A6%BC%EA%A6%B1%EA%A6%B6%EA%A6%B1%EA%A6%B6%EA%A6%82%EA%A6%92%EA%A6%BA%EA%A6%B4%EA%A6%A5%EA%A6%B6%EA%A6%A0%EA%A7%80%20Malang</t>
+          <t>https://www.instagram.com/p/CUOvwjVPKUh/</t>
         </is>
       </c>
     </row>
@@ -17086,16 +17040,16 @@
         </is>
       </c>
       <c r="I371" t="n">
-        <v>3500</v>
+        <v>0</v>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Puncak%20Kapur%20Segaran%20Malang</t>
+          <t>https://www.instagram.com/p/Cz5ZIOGrwK0/</t>
         </is>
       </c>
     </row>
@@ -17223,11 +17177,7 @@
       <c r="I374" t="n">
         <v>0</v>
       </c>
-      <c r="J374" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
@@ -17264,11 +17214,7 @@
       <c r="I375" t="n">
         <v>0</v>
       </c>
-      <c r="J375" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
@@ -17753,16 +17699,16 @@
         </is>
       </c>
       <c r="I386" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20TPU%20Kasin%20Malang</t>
+          <t>https://www.instagram.com/p/DBaaoW0y2w1/</t>
         </is>
       </c>
     </row>
@@ -17800,11 +17746,7 @@
       <c r="I387" t="n">
         <v>0</v>
       </c>
-      <c r="J387" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J387" t="inlineStr"/>
       <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
@@ -17929,16 +17871,16 @@
         </is>
       </c>
       <c r="I390" t="n">
-        <v>108000</v>
+        <v>0</v>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>telkomsel.com</t>
+          <t>malangkota.go.id</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>https://www.telkomsel.com/jelajah/jelajah-lifestyle/7-tempat-wisata-di-malang-yang-lagi-hits-dan-murah</t>
+          <t>https://malangkota.go.id/taman-dan-hutan-kota/</t>
         </is>
       </c>
     </row>
@@ -17974,16 +17916,16 @@
         </is>
       </c>
       <c r="I391" t="n">
-        <v>294030</v>
+        <v>0</v>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>traveloka.com</t>
+          <t>bromoindonesia.com</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>https://www.traveloka.com/id-id/activities/indonesia/product/mount-bromo-tour-departure-from-malang-1-day-2000914428209</t>
+          <t>https://bromoindonesia.com/</t>
         </is>
       </c>
     </row>
@@ -18021,11 +17963,7 @@
       <c r="I392" t="n">
         <v>0</v>
       </c>
-      <c r="J392" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J392" t="inlineStr"/>
       <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
@@ -18152,11 +18090,7 @@
       <c r="I395" t="n">
         <v>0</v>
       </c>
-      <c r="J395" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
@@ -18326,16 +18260,16 @@
         </is>
       </c>
       <c r="I399" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>24travel.id</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Museum%20Mpu%20Purwa%20Malang</t>
+          <t>https://24travel.id/museum-mpu-purwa-malang/</t>
         </is>
       </c>
     </row>
@@ -18371,16 +18305,16 @@
         </is>
       </c>
       <c r="I400" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>dlh.malangkota.go.id</t>
         </is>
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Taman%20Kebun%20Bibit%20Mojolangu%20Kota%20Malang%20Malang</t>
+          <t>https://dlh.malangkota.go.id/dokumen/data-taman-aktif-dan-kebun-bibit/</t>
         </is>
       </c>
     </row>
@@ -19001,7 +18935,7 @@
         </is>
       </c>
       <c r="I414" t="n">
-        <v>250000</v>
+        <v>130000</v>
       </c>
       <c r="J414" t="inlineStr">
         <is>
@@ -19496,7 +19430,7 @@
         </is>
       </c>
       <c r="I425" t="n">
-        <v>135000</v>
+        <v>15000</v>
       </c>
       <c r="J425" t="inlineStr">
         <is>
@@ -19901,16 +19835,16 @@
         </is>
       </c>
       <c r="I434" t="n">
-        <v>180000</v>
+        <v>0</v>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Rest%20Area%20Pletes%20Malang</t>
+          <t>https://id.trip.com/travel-guide/attraction/sumbermanjing-wetan/rest-area-pletes-142454099/</t>
         </is>
       </c>
     </row>
@@ -19946,16 +19880,16 @@
         </is>
       </c>
       <c r="I435" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>perhutani.co.id</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Rest%20Area%20Druju%20Malang</t>
+          <t>https://www.perhutani.co.id/perhutani-bangun-rest-area-di-druju/</t>
         </is>
       </c>
     </row>
@@ -19993,11 +19927,7 @@
       <c r="I436" t="n">
         <v>0</v>
       </c>
-      <c r="J436" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J436" t="inlineStr"/>
       <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
@@ -20124,11 +20054,7 @@
       <c r="I439" t="n">
         <v>0</v>
       </c>
-      <c r="J439" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J439" t="inlineStr"/>
       <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
@@ -20388,16 +20314,16 @@
         </is>
       </c>
       <c r="I445" t="n">
-        <v>220748</v>
+        <v>0</v>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>indonesiana.id</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Dam%20tawang%20rejeni%20Malang</t>
+          <t>https://www.indonesiana.id/read/184962/pesona-sabana-rejeni-rinjani-nya-malang-selatan</t>
         </is>
       </c>
     </row>
@@ -20568,16 +20494,16 @@
         </is>
       </c>
       <c r="I449" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>traveloka.com</t>
         </is>
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Parkir%20mobil%20gratis%20Masjid%20tiban%20turen%20Malang</t>
+          <t>https://www.traveloka.com/id-id/explore/destination/masjid-tiban-turen-malang-trp/483103</t>
         </is>
       </c>
     </row>
@@ -20703,16 +20629,16 @@
         </is>
       </c>
       <c r="I452" t="n">
-        <v>5000</v>
+        <v>150000</v>
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Sumber%20Buntung%20Wisata%20air%20alami%20urek%20urek%20Malang</t>
+          <t>https://id.trip.com/travel-guide/attraction/bantur/wisata-sumber-buntung-138910276/</t>
         </is>
       </c>
     </row>
@@ -20928,16 +20854,16 @@
         </is>
       </c>
       <c r="I457" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Masjid%20Tiban%20Malang%20Malang</t>
+          <t>https://id.trip.com/travel-guide/attraction/turen/masjid-tiban-144255829</t>
         </is>
       </c>
     </row>
@@ -21107,19 +21033,9 @@
           <t>https://www.google.com/maps/place/OG+Durian/data=!4m7!3m6!1s0x2dd621f90e1eb803:0x2676277a2feca1ab!8m2!3d-8.1306309!4d112.663318!16s%2Fg%2F11y28pd1m5!19sChIJA7geDvkh1i0Rq6HsL3ondiY?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I461" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J461" t="inlineStr">
-        <is>
-          <t>Google Snippet</t>
-        </is>
-      </c>
-      <c r="K461" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20OG%20Durian%20Malang</t>
-        </is>
-      </c>
+      <c r="I461" t="inlineStr"/>
+      <c r="J461" t="inlineStr"/>
+      <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -21697,12 +21613,12 @@
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>instagram.com</t>
+          <t>24travel.id</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DVLdayUkzOx/</t>
+          <t>https://24travel.id/batu-ekonomis-park/?srsltid=AfmBOoqJj1z5sZw7WpUwSiWpCAFAnpXCHMumgrP3UKgFApN18Mvtjj5_</t>
         </is>
       </c>
     </row>
@@ -21782,19 +21698,9 @@
           <t>https://www.google.com/maps/place/Patung+Singo+Edan+Arema/data=!4m7!3m6!1s0x2dd6283c114bacbf:0xd0aefdd0b4975b22!8m2!3d-7.977314!4d112.6366485!16s%2Fg%2F11cjhc28p6!19sChIJv6xLETwo1i0RIluXtND9rtA?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I476" t="n">
-        <v>2000</v>
-      </c>
-      <c r="J476" t="inlineStr">
-        <is>
-          <t>Google Snippet</t>
-        </is>
-      </c>
-      <c r="K476" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Patung%20Singo%20Edan%20Arema%20Malang</t>
-        </is>
-      </c>
+      <c r="I476" t="inlineStr"/>
+      <c r="J476" t="inlineStr"/>
+      <c r="K476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -21873,16 +21779,16 @@
         </is>
       </c>
       <c r="I478" t="n">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>malangraya.pikiran-rakyat.com</t>
         </is>
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Lapangan%20Rampal%20Malang</t>
+          <t>https://malangraya.pikiran-rakyat.com/kota-malang/pr-3627757714/harga-tiket-taman-rampal-wisata-ramah-anak-terbaru-di-malang</t>
         </is>
       </c>
     </row>
@@ -22008,7 +21914,7 @@
         </is>
       </c>
       <c r="I481" t="n">
-        <v>280000</v>
+        <v>250000</v>
       </c>
       <c r="J481" t="inlineStr">
         <is>
@@ -22367,19 +22273,9 @@
           <t>https://www.google.com/maps/place/Taman+Indragiri+Malang/data=!4m7!3m6!1s0x2dd62929a77d982f:0x9f7967fe98455e65!8m2!3d-7.9580063!4d112.6418657!16s%2Fg%2F11jv1gnwr0!19sChIJL5h9pykp1i0RZV5FmP5neZ8?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I489" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J489" t="inlineStr">
-        <is>
-          <t>Google Snippet</t>
-        </is>
-      </c>
-      <c r="K489" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Taman%20Indragiri%20Malang%20Malang</t>
-        </is>
-      </c>
+      <c r="I489" t="inlineStr"/>
+      <c r="J489" t="inlineStr"/>
+      <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -22458,16 +22354,16 @@
         </is>
       </c>
       <c r="I491" t="n">
-        <v>2000</v>
+        <v>15000</v>
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>traveloka.com</t>
         </is>
       </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Hutan%20Kota%20Polowijen%20Malang</t>
+          <t>https://www.traveloka.com/id-id/explore/activities/tempat-wisata-di-malang-yang-murah-ta/532297</t>
         </is>
       </c>
     </row>
@@ -22547,19 +22443,9 @@
           <t>https://www.google.com/maps/place/Taman+Sulfat+Boulevard/data=!4m7!3m6!1s0x2dd6284c9f6e7ac5:0x911cecac7fa1480e!8m2!3d-7.961751!4d112.649904!16s%2Fg%2F11b6hxv0cd!19sChIJxXpun0wo1i0RDkihf6zsHJE?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I493" t="n">
-        <v>100000</v>
-      </c>
-      <c r="J493" t="inlineStr">
-        <is>
-          <t>Google Snippet</t>
-        </is>
-      </c>
-      <c r="K493" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Taman%20Sulfat%20Boulevard%20Malang</t>
-        </is>
-      </c>
+      <c r="I493" t="inlineStr"/>
+      <c r="J493" t="inlineStr"/>
+      <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -22592,19 +22478,9 @@
           <t>https://www.google.com/maps/place/Kebun+Murbei/data=!4m7!3m6!1s0x2dd629b2b3433015:0x424742adf4ac410d!8m2!3d-7.9306506!4d112.6608826!16s%2Fg%2F11qfxh8vdz!19sChIJFTBDs7Ip1i0RDUGs9K1CR0I?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I494" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J494" t="inlineStr">
-        <is>
-          <t>Google Snippet</t>
-        </is>
-      </c>
-      <c r="K494" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Kebun%20Murbei%20Malang</t>
-        </is>
-      </c>
+      <c r="I494" t="inlineStr"/>
+      <c r="J494" t="inlineStr"/>
+      <c r="K494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -22772,19 +22648,9 @@
           <t>https://www.google.com/maps/place/SANGGAR+SEMAR/data=!4m7!3m6!1s0x2dd6293b9f78576f:0x8d83d3ce8708872d!8m2!3d-7.9276929!4d112.6554293!16s%2Fg%2F11vbttyqdk!19sChIJb1d4nzsp1i0RLYcIh87Tg40?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I498" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J498" t="inlineStr">
-        <is>
-          <t>Google Snippet</t>
-        </is>
-      </c>
-      <c r="K498" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20SANGGAR%20SEMAR%20Malang</t>
-        </is>
-      </c>
+      <c r="I498" t="inlineStr"/>
+      <c r="J498" t="inlineStr"/>
+      <c r="K498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -22908,16 +22774,16 @@
         </is>
       </c>
       <c r="I501" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>youtube.com</t>
         </is>
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Kebon%20Winih%20Randuagung%20Malang</t>
+          <t>https://www.youtube.com/watch?v=LxUxGN1moMk</t>
         </is>
       </c>
     </row>
@@ -22952,19 +22818,9 @@
           <t>https://www.google.com/maps/place/Wisata+Sumbersuko,+Randuagung/data=!4m7!3m6!1s0x2dd62b22c9e30eaf:0x5b540d1d64a25ba1!8m2!3d-7.8562826!4d112.6782911!16s%2Fg%2F11d_d1jsf3!19sChIJrw7jySIr1i0RoVuiZB0NVFs?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I502" t="n">
-        <v>5000</v>
-      </c>
-      <c r="J502" t="inlineStr">
-        <is>
-          <t>Google Snippet</t>
-        </is>
-      </c>
-      <c r="K502" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Wisata%20Sumbersuko%2C%20Randuagung%20Malang</t>
-        </is>
-      </c>
+      <c r="I502" t="inlineStr"/>
+      <c r="J502" t="inlineStr"/>
+      <c r="K502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -23088,16 +22944,16 @@
         </is>
       </c>
       <c r="I505" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Taman%20Wisata%20Polamanku%20Malang</t>
+          <t>https://www.instagram.com/reel/DEjhXj4TVRk/</t>
         </is>
       </c>
     </row>
@@ -23222,19 +23078,9 @@
           <t>https://www.google.com/maps/place/Rest+Area+84B+Malang+Strudel+Playland/data=!4m7!3m6!1s0x2dd62b001742429d:0x84beee5003f64a4e!8m2!3d-7.897184!4d112.6965623!16s%2Fg%2F11yz7q2hyh!19sChIJnUJCFwAr1i0RTkr2A1DuvoQ?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I508" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J508" t="inlineStr">
-        <is>
-          <t>Google Snippet</t>
-        </is>
-      </c>
-      <c r="K508" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Rest%20Area%2084B%20Malang%20Strudel%20Playland%20Malang</t>
-        </is>
-      </c>
+      <c r="I508" t="inlineStr"/>
+      <c r="J508" t="inlineStr"/>
+      <c r="K508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -23312,19 +23158,9 @@
           <t>https://www.google.com/maps/place/Museum+Ganesya+%28Gelar+Indonesia+Budaya%29/data=!4m7!3m6!1s0x2dd62959389fa867:0xa8ff9920f9b8b3b9!8m2!3d-7.9231883!4d112.6570604!16s%2Fg%2F11hyr1z6q8!19sChIJZ6ifOFkp1i0RubO4-SCZ_6g?authuser=0&amp;hl=id&amp;rclk=1</t>
         </is>
       </c>
-      <c r="I510" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J510" t="inlineStr">
-        <is>
-          <t>Google Snippet</t>
-        </is>
-      </c>
-      <c r="K510" t="inlineStr">
-        <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Museum%20Ganesya%20%28Gelar%20Indonesia%20Budaya%29%20Malang</t>
-        </is>
-      </c>
+      <c r="I510" t="inlineStr"/>
+      <c r="J510" t="inlineStr"/>
+      <c r="K510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -23358,16 +23194,16 @@
         </is>
       </c>
       <c r="I511" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K511" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Kebun%20Opa%20Malang</t>
+          <t>https://www.instagram.com/kebunopakarangkunci/</t>
         </is>
       </c>
     </row>
@@ -23540,11 +23376,7 @@
       <c r="I515" t="n">
         <v>0</v>
       </c>
-      <c r="J515" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J515" t="inlineStr"/>
       <c r="K515" t="inlineStr"/>
     </row>
     <row r="516">
@@ -23581,11 +23413,7 @@
       <c r="I516" t="n">
         <v>0</v>
       </c>
-      <c r="J516" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr"/>
     </row>
     <row r="517">
@@ -23755,16 +23583,16 @@
         </is>
       </c>
       <c r="I520" t="n">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>mocca.studio</t>
         </is>
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20KEK%20Singhasari%20Malang</t>
+          <t>https://mocca.studio/</t>
         </is>
       </c>
     </row>
@@ -23845,16 +23673,16 @@
         </is>
       </c>
       <c r="I522" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>kompasiana.com</t>
         </is>
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Wisata%20Latar%20Bale%20Malang</t>
+          <t>https://www.kompasiana.com/nooraidilfitri5383/66ad84ed34777c31f4176972/simak-kondisi-wisata-latar-bale-setelah-2-tahun-diresmikan-jadi-pusat-edukasi-hingga-budidaya-ikan</t>
         </is>
       </c>
     </row>
@@ -23894,12 +23722,12 @@
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20VNR%20Malang</t>
+          <t>https://www.instagram.com/beachpool_09/</t>
         </is>
       </c>
     </row>
@@ -24070,16 +23898,16 @@
         </is>
       </c>
       <c r="I527" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>traveloka.com</t>
         </is>
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Sumber%20Waras%20Malang</t>
+          <t>https://www.traveloka.com/id-id/explore/destination/kebun-teh-lawang-trp/356120</t>
         </is>
       </c>
     </row>
@@ -24565,16 +24393,16 @@
         </is>
       </c>
       <c r="I538" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K538" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Taman%20Aglaonema%20Dampit%20Malang</t>
+          <t>https://id.trip.com/travel-guide/attraction/dampit/taman-aglaonema-dampit-142608230</t>
         </is>
       </c>
     </row>
@@ -24880,16 +24708,16 @@
         </is>
       </c>
       <c r="I545" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>jadesta.kemenpar.go.id</t>
         </is>
       </c>
       <c r="K545" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Desa%20Wisata%20Sidorejo%20Indah%20%28%20Dewi%20Sri%20%29%20Malang</t>
+          <t>https://jadesta.kemenpar.go.id/desa/sidorejo_indah_dewi_sri</t>
         </is>
       </c>
     </row>
@@ -24974,12 +24802,12 @@
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>24travel.id</t>
         </is>
       </c>
       <c r="K547" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Museum%20Panji%20Malang</t>
+          <t>https://24travel.id/museum-panji-malang/</t>
         </is>
       </c>
     </row>
@@ -25240,16 +25068,16 @@
         </is>
       </c>
       <c r="I553" t="n">
-        <v>25000</v>
+        <v>7000</v>
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>traveloka.com</t>
         </is>
       </c>
       <c r="K553" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Pura%20Luhur%20Dwijawarsa%20Malang</t>
+          <t>https://www.traveloka.com/id-id/explore/activities/pura-di-malang-ta/505352</t>
         </is>
       </c>
     </row>
@@ -25600,16 +25428,16 @@
         </is>
       </c>
       <c r="I561" t="n">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K561" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Taman%20Suwida%20Malang</t>
+          <t>https://id.trip.com/travel-guide/attraction/pakis/taman-suwida-136730844/</t>
         </is>
       </c>
     </row>
@@ -25690,16 +25518,16 @@
         </is>
       </c>
       <c r="I563" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>tripwisatabromo.com</t>
+          <t>paketwisatabromo.co.id</t>
         </is>
       </c>
       <c r="K563" t="inlineStr">
         <is>
-          <t>https://tripwisatabromo.com/artikel/paralayang-batu-malang/</t>
+          <t>https://www.paketwisatabromo.co.id/paralayang-sidoluhur-lawang/</t>
         </is>
       </c>
     </row>
@@ -25960,16 +25788,16 @@
         </is>
       </c>
       <c r="I569" t="n">
-        <v>125000</v>
+        <v>0</v>
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>instagram.com</t>
+          <t>matic.malangkab.go.id</t>
         </is>
       </c>
       <c r="K569" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ps.mangundharma/</t>
+          <t>https://matic.malangkab.go.id/listing/padepokan-seni-mangun-dharmo-tumpang</t>
         </is>
       </c>
     </row>
@@ -26007,11 +25835,7 @@
       <c r="I570" t="n">
         <v>0</v>
       </c>
-      <c r="J570" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="J570" t="inlineStr"/>
       <c r="K570" t="inlineStr"/>
     </row>
     <row r="571">
@@ -26046,16 +25870,16 @@
         </is>
       </c>
       <c r="I571" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="J571" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K571" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Taman%20Durian%20Pak%20Peno%20Malang</t>
+          <t>https://www.instagram.com/reel/DSwJxb1k2Vm/</t>
         </is>
       </c>
     </row>
@@ -26181,16 +26005,16 @@
         </is>
       </c>
       <c r="I574" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>instagram.com</t>
         </is>
       </c>
       <c r="K574" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Taman%20Buah%20Jeru%20Tumpang%20Malang</t>
+          <t>https://www.instagram.com/reel/DExEKcku9m7/</t>
         </is>
       </c>
     </row>
@@ -26721,16 +26545,16 @@
         </is>
       </c>
       <c r="I586" t="n">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="J586" t="inlineStr">
         <is>
-          <t>paketwisatabromo.co.id</t>
+          <t>jadesta.kemenpar.go.id</t>
         </is>
       </c>
       <c r="K586" t="inlineStr">
         <is>
-          <t>https://www.paketwisatabromo.co.id/wisata-kampoeng-banyu/</t>
+          <t>https://jadesta.kemenpar.go.id/atraksi/river_tubing_banyumaro</t>
         </is>
       </c>
     </row>
@@ -26946,16 +26770,16 @@
         </is>
       </c>
       <c r="I591" t="n">
-        <v>294030</v>
+        <v>0</v>
       </c>
       <c r="J591" t="inlineStr">
         <is>
-          <t>traveloka.com</t>
+          <t>abimanyutravel.id</t>
         </is>
       </c>
       <c r="K591" t="inlineStr">
         <is>
-          <t>https://www.traveloka.com/id-id/activities/indonesia/product/mount-bromo-tour-departure-from-malang-1-day-2000914428209</t>
+          <t>https://www.abimanyutravel.id/paket-wisata-bromo</t>
         </is>
       </c>
     </row>
@@ -27981,16 +27805,16 @@
         </is>
       </c>
       <c r="I614" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="J614" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>malangstrudel.com</t>
         </is>
       </c>
       <c r="K614" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Air%20Terjun%20Telaga%20Warna%20Malang</t>
+          <t>https://malangstrudel.com/eksotika-air-terjun-telaga-warna-malang.html</t>
         </is>
       </c>
     </row>
@@ -28521,16 +28345,16 @@
         </is>
       </c>
       <c r="I626" t="n">
-        <v>275000</v>
+        <v>0</v>
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>Google Snippet</t>
+          <t>id.trip.com</t>
         </is>
       </c>
       <c r="K626" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?q=Harga%20tiket%20masuk%20Pondok%20banteng%20Malang</t>
+          <t>https://id.trip.com/travel-guide/attraction/ampelgading/pondok-banteng-150704589</t>
         </is>
       </c>
     </row>
